--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N100_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N100_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.99758671461929</v>
+        <v>12.51210784112564</v>
       </c>
       <c r="D2" t="n">
-        <v>75.34771074334333</v>
+        <v>12.24400299579329</v>
       </c>
       <c r="E2" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F2" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.98146086409872</v>
+        <v>11.53448739041604</v>
       </c>
       <c r="D3" t="n">
-        <v>70.15309662018612</v>
+        <v>11.39987820078025</v>
       </c>
       <c r="E3" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F3" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.23397641622961</v>
+        <v>11.57552116763731</v>
       </c>
       <c r="D4" t="n">
-        <v>69.51160524723529</v>
+        <v>11.29563585267574</v>
       </c>
       <c r="E4" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F4" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.69852619946126</v>
+        <v>10.02601050741245</v>
       </c>
       <c r="D5" t="n">
-        <v>60.42124875150913</v>
+        <v>9.818452922120235</v>
       </c>
       <c r="E5" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F5" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>74.64689357951376</v>
+        <v>12.13012020667099</v>
       </c>
       <c r="D6" t="n">
-        <v>74.02147234036076</v>
+        <v>12.02848925530862</v>
       </c>
       <c r="E6" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F6" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.07084469280407</v>
+        <v>9.599012262580661</v>
       </c>
       <c r="D7" t="n">
-        <v>57.33764787045072</v>
+        <v>9.317367778948244</v>
       </c>
       <c r="E7" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F7" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>70.98793078050284</v>
+        <v>11.53553875183171</v>
       </c>
       <c r="D8" t="n">
-        <v>69.23149416150389</v>
+        <v>11.25011780124438</v>
       </c>
       <c r="E8" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F8" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.2033943452808</v>
+        <v>5.23305158110813</v>
       </c>
       <c r="D9" t="n">
-        <v>31.40817113134084</v>
+        <v>5.103827808842887</v>
       </c>
       <c r="E9" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F9" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68940343900615</v>
+        <v>8.074528058838499</v>
       </c>
       <c r="D10" t="n">
-        <v>50.14184202583811</v>
+        <v>8.148049329198694</v>
       </c>
       <c r="E10" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F10" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.51488263878629</v>
+        <v>2.521168428802772</v>
       </c>
       <c r="D11" t="n">
-        <v>14.41543725018254</v>
+        <v>2.342508553154663</v>
       </c>
       <c r="E11" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F11" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.60778382668704</v>
+        <v>7.898764871836645</v>
       </c>
       <c r="D12" t="n">
-        <v>49.36707984169897</v>
+        <v>8.022150474276083</v>
       </c>
       <c r="E12" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F12" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>55.02328800844359</v>
+        <v>8.941284301372082</v>
       </c>
       <c r="D13" t="n">
-        <v>53.67103036979304</v>
+        <v>8.72154243509137</v>
       </c>
       <c r="E13" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F13" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.19286052689373</v>
+        <v>4.906339835620231</v>
       </c>
       <c r="D14" t="n">
-        <v>28.75350379577487</v>
+        <v>4.672444366813417</v>
       </c>
       <c r="E14" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F14" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>65.47642333562258</v>
+        <v>10.63991879203867</v>
       </c>
       <c r="D15" t="n">
-        <v>64.21389119521471</v>
+        <v>10.43475731922239</v>
       </c>
       <c r="E15" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F15" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.17904097661076</v>
+        <v>6.041594158699249</v>
       </c>
       <c r="D16" t="n">
-        <v>35.84025642393815</v>
+        <v>5.82404166888995</v>
       </c>
       <c r="E16" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F16" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.1991994179558</v>
+        <v>7.182369905417819</v>
       </c>
       <c r="D17" t="n">
-        <v>45.19313059522884</v>
+        <v>7.343883721724686</v>
       </c>
       <c r="E17" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F17" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>5.444845794210185</v>
+        <v>0.884787441559155</v>
       </c>
       <c r="D18" t="n">
-        <v>5.147549044550352</v>
+        <v>0.8364767197394322</v>
       </c>
       <c r="E18" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F18" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>49.62732411573515</v>
+        <v>8.064440168806962</v>
       </c>
       <c r="D19" t="n">
-        <v>50.9890907914931</v>
+        <v>8.28572725361763</v>
       </c>
       <c r="E19" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F19" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>9.595941801223518</v>
+        <v>1.559340542698822</v>
       </c>
       <c r="D20" t="n">
-        <v>10.38265765623768</v>
+        <v>1.687181869138623</v>
       </c>
       <c r="E20" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F20" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>52.69250899672352</v>
+        <v>8.562532711967572</v>
       </c>
       <c r="D21" t="n">
-        <v>51.79921712627171</v>
+        <v>8.417372783019154</v>
       </c>
       <c r="E21" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F21" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>33.57625824240333</v>
+        <v>5.45614196439054</v>
       </c>
       <c r="D22" t="n">
-        <v>35.14851687648117</v>
+        <v>5.711633992428191</v>
       </c>
       <c r="E22" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F22" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>46.12448835428372</v>
+        <v>7.495229357571104</v>
       </c>
       <c r="D23" t="n">
-        <v>47.68721156181756</v>
+        <v>7.749171878795353</v>
       </c>
       <c r="E23" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F23" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>15.58009662917292</v>
+        <v>2.5317657022406</v>
       </c>
       <c r="D24" t="n">
-        <v>17.01806855692077</v>
+        <v>2.765436140499625</v>
       </c>
       <c r="E24" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F24" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>59.94568977525736</v>
+        <v>9.741174588479321</v>
       </c>
       <c r="D25" t="n">
-        <v>59.42866962739886</v>
+        <v>9.657158814452314</v>
       </c>
       <c r="E25" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F25" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>28.15491815419823</v>
+        <v>4.575174200057213</v>
       </c>
       <c r="D26" t="n">
-        <v>28.8818200137337</v>
+        <v>4.693295752231727</v>
       </c>
       <c r="E26" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F26" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>27.22381920678398</v>
+        <v>4.423870621102396</v>
       </c>
       <c r="D27" t="n">
-        <v>28.75506658783176</v>
+        <v>4.672698320522661</v>
       </c>
       <c r="E27" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F27" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>84.34872633752195</v>
+        <v>13.70666802984732</v>
       </c>
       <c r="D28" t="n">
-        <v>85.91835433495676</v>
+        <v>13.96173257943047</v>
       </c>
       <c r="E28" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F28" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>61.36032917741548</v>
+        <v>9.971053491330016</v>
       </c>
       <c r="D29" t="n">
-        <v>61.14399321889557</v>
+        <v>9.935898898070532</v>
       </c>
       <c r="E29" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F29" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>36.28452090922899</v>
+        <v>5.896234647749711</v>
       </c>
       <c r="D30" t="n">
-        <v>37.49899008258065</v>
+        <v>6.093585888419355</v>
       </c>
       <c r="E30" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F30" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>43.76836442117056</v>
+        <v>7.112359218440216</v>
       </c>
       <c r="D31" t="n">
-        <v>45.20308394351899</v>
+        <v>7.345501140821836</v>
       </c>
       <c r="E31" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F31" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>63.5905802922849</v>
+        <v>10.3334692974963</v>
       </c>
       <c r="D32" t="n">
-        <v>63.82483252291168</v>
+        <v>10.37153528497315</v>
       </c>
       <c r="E32" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F32" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>52.40823039684651</v>
+        <v>8.516337439487559</v>
       </c>
       <c r="D33" t="n">
-        <v>53.32596355704101</v>
+        <v>8.665469078019164</v>
       </c>
       <c r="E33" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F33" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>63.20102223334086</v>
+        <v>10.27016611291789</v>
       </c>
       <c r="D34" t="n">
-        <v>63.61983780032936</v>
+        <v>10.33822364255352</v>
       </c>
       <c r="E34" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F34" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>74.56740814025625</v>
+        <v>12.11720382279164</v>
       </c>
       <c r="D35" t="n">
-        <v>76.32608802659475</v>
+        <v>12.40298930432165</v>
       </c>
       <c r="E35" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F35" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>97.61505682234888</v>
+        <v>15.86244673363169</v>
       </c>
       <c r="D36" t="n">
-        <v>99.34308409750523</v>
+        <v>16.1432511658446</v>
       </c>
       <c r="E36" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F36" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>59.34491492664748</v>
+        <v>9.643548675580215</v>
       </c>
       <c r="D37" t="n">
-        <v>60.89295972798094</v>
+        <v>9.895105955796902</v>
       </c>
       <c r="E37" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F37" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>74.52752411836099</v>
+        <v>12.11072266923366</v>
       </c>
       <c r="D38" t="n">
-        <v>76.30051626658384</v>
+        <v>12.39883389331987</v>
       </c>
       <c r="E38" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F38" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>66.60694459906668</v>
+        <v>10.82362849734834</v>
       </c>
       <c r="D39" t="n">
-        <v>68.33171434028269</v>
+        <v>11.10390358029594</v>
       </c>
       <c r="E39" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F39" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>85.58527714008504</v>
+        <v>13.90760753526382</v>
       </c>
       <c r="D40" t="n">
-        <v>87.35791793000746</v>
+        <v>14.19566166362621</v>
       </c>
       <c r="E40" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F40" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>75.26198413647998</v>
+        <v>12.230072422178</v>
       </c>
       <c r="D41" t="n">
-        <v>77.0161395164321</v>
+        <v>12.51512267142022</v>
       </c>
       <c r="E41" t="n">
-        <v>21.59670275665282</v>
+        <v>3.509464197956084</v>
       </c>
       <c r="F41" t="n">
-        <v>21.68836062525761</v>
+        <v>3.524358601604363</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
